--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1507-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1507-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6704419F-9797-4FA1-8E05-0E4C90525D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B66814E7-CD85-4CD0-884E-E38CF1FFDAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{62D4B678-66D7-4364-B937-3C2746CA421C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{91D37730-F402-4E28-8AF7-28A5E58A23D8}"/>
   </bookViews>
   <sheets>
     <sheet name="1507-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1586,26 +1586,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F802C2C2-ACD4-440D-B93B-9C031B0CFC2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FED5C8D6-09AF-43CA-AA9C-286B696F6E14}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6" customWidth="1"/>
-    <col min="7" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1639,7 +1638,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1675,7 +1674,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1727,7 +1726,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1795,7 +1794,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2021</v>
       </c>
@@ -1867,7 +1866,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2020</v>
       </c>
@@ -1939,7 +1938,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2019</v>
       </c>
@@ -2011,7 +2010,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2018</v>
       </c>
@@ -2083,7 +2082,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2017</v>
       </c>
@@ -2155,7 +2154,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2016</v>
       </c>
@@ -2227,7 +2226,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2015</v>
       </c>
@@ -2299,7 +2298,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2014</v>
       </c>
@@ -2371,7 +2370,7 @@
         <v>7.16</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2013</v>
       </c>
@@ -2443,7 +2442,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2012</v>
       </c>
@@ -2515,7 +2514,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2011</v>
       </c>
@@ -2587,7 +2586,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2010</v>
       </c>
@@ -2659,7 +2658,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2009</v>
       </c>
@@ -2731,7 +2730,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2008</v>
       </c>
@@ -2803,7 +2802,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2007</v>
       </c>
@@ -2875,7 +2874,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2006</v>
       </c>
@@ -2947,7 +2946,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2005</v>
       </c>
@@ -3019,7 +3018,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2004</v>
       </c>
@@ -3091,7 +3090,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2003</v>
       </c>
@@ -3163,7 +3162,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2002</v>
       </c>
@@ -3235,7 +3234,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2001</v>
       </c>
@@ -3307,7 +3306,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2000</v>
       </c>
@@ -3379,7 +3378,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>1999</v>
       </c>
@@ -3451,7 +3450,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>1998</v>
       </c>
@@ -3523,7 +3522,7 @@
         <v>8.06</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>1997</v>
       </c>
@@ -3595,7 +3594,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="41">
         <v>1996</v>
       </c>
@@ -3667,7 +3666,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="43"/>
       <c r="B31" s="44"/>
       <c r="C31" s="18" t="s">
@@ -3695,7 +3694,7 @@
       <c r="W31" s="50"/>
       <c r="X31" s="46"/>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="51">
         <v>1995</v>
       </c>
@@ -3767,7 +3766,7 @@
         <v>6.14</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="53"/>
       <c r="B33" s="54"/>
       <c r="C33" s="20" t="s">
@@ -3795,7 +3794,7 @@
       <c r="W33" s="60"/>
       <c r="X33" s="56"/>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="41">
         <v>1994</v>
       </c>
@@ -3867,7 +3866,7 @@
         <v>7.21</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="43"/>
       <c r="B35" s="44"/>
       <c r="C35" s="18" t="s">
@@ -3895,7 +3894,7 @@
       <c r="W35" s="50"/>
       <c r="X35" s="46"/>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>1993</v>
       </c>
@@ -3967,7 +3966,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="41">
         <v>1992</v>
       </c>
@@ -4039,7 +4038,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="43"/>
       <c r="B38" s="44"/>
       <c r="C38" s="18" t="s">
@@ -4067,7 +4066,7 @@
       <c r="W38" s="50"/>
       <c r="X38" s="46"/>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="51">
         <v>1991</v>
       </c>
@@ -4139,7 +4138,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="53"/>
       <c r="B40" s="54"/>
       <c r="C40" s="20" t="s">
@@ -4167,7 +4166,7 @@
       <c r="W40" s="60"/>
       <c r="X40" s="56"/>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>1990</v>
       </c>
@@ -4239,7 +4238,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>1989</v>
       </c>
@@ -4311,7 +4310,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>1988</v>
       </c>
@@ -4383,7 +4382,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>1987</v>
       </c>
@@ -4455,7 +4454,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39">
         <v>1986</v>
       </c>
@@ -4527,7 +4526,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>1985</v>
       </c>
@@ -4599,7 +4598,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39" t="s">
         <v>64</v>
       </c>
